--- a/tame_output/ON/bt/strategyON_20240226.xlsx
+++ b/tame_output/ON/bt/strategyON_20240226.xlsx
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-21.9%</t>
+          <t>-21.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>95.6%</t>
+          <t>95.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>1.396982224666362</v>
+        <v>1.397674563238803</v>
       </c>
       <c r="E1885" t="n">
-        <v>3.720190641003945</v>
+        <v>3.720467576432921</v>
       </c>
       <c r="F1885" t="n">
-        <v>2.45106353381656</v>
+        <v>2.45117876202869</v>
       </c>
       <c r="G1885" t="n">
-        <v>4.632392295741084</v>
+        <v>4.632461432668362</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240226.xlsx
+++ b/tame_output/ON/bt/strategyON_20240226.xlsx
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153005</v>
+        <v>3.258791981153006</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537424</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074619</v>
+        <v>3.25147557607462</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911637</v>
+        <v>3.233800325911638</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213493</v>
+        <v>3.223539378213494</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416042</v>
+        <v>3.231167537416043</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382326</v>
+        <v>3.235981977382327</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495498</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178245</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207814</v>
+        <v>3.305316798207815</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310983</v>
+        <v>3.284619513310984</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006534</v>
+        <v>3.305849539006535</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309426</v>
+        <v>3.311086391309427</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970907</v>
+        <v>3.304715716970908</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330525</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.30261819419174</v>
+        <v>3.302618194191741</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108642</v>
+        <v>3.305023265108643</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.37443904309412</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.40596051119929</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969598</v>
+        <v>3.424633354969599</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923091</v>
+        <v>3.419979433923092</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297754</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234393</v>
+        <v>3.480688917234394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860582</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.317290694012511</v>
+        <v>3.317290694012512</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>1.397674563238803</v>
+        <v>1.397782859875581</v>
       </c>
       <c r="E1885" t="n">
-        <v>3.720467576432921</v>
+        <v>3.720510895087632</v>
       </c>
       <c r="F1885" t="n">
-        <v>2.45117876202869</v>
+        <v>2.450951804238153</v>
       </c>
       <c r="G1885" t="n">
-        <v>4.632461432668362</v>
+        <v>4.632325257994039</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240226.xlsx
+++ b/tame_output/ON/bt/strategyON_20240226.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>447.6%</t>
+          <t>448.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-21.8%</t>
+          <t>-27.3%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>94.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-18.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-6.4%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,27 +1323,27 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>71.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>24.4%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>132.8%</t>
+          <t>133.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>126.3%</t>
+          <t>127.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>19.2%</t>
         </is>
       </c>
     </row>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153006</v>
+        <v>3.258791981153005</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537424</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.25147557607462</v>
+        <v>3.251475576074619</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911638</v>
+        <v>3.233800325911637</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213494</v>
+        <v>3.223539378213493</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416043</v>
+        <v>3.231167537416042</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382327</v>
+        <v>3.235981977382326</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.278199702495498</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178245</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207815</v>
+        <v>3.305316798207814</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310984</v>
+        <v>3.284619513310983</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006535</v>
+        <v>3.305849539006534</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309427</v>
+        <v>3.311086391309426</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970908</v>
+        <v>3.304715716970907</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330525</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191741</v>
+        <v>3.30261819419174</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108643</v>
+        <v>3.305023265108642</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309412</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119929</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969599</v>
+        <v>3.424633354969598</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923092</v>
+        <v>3.419979433923091</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297754</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737173</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234394</v>
+        <v>3.480688917234393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860583</v>
+        <v>3.493712438860582</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.317290694012512</v>
+        <v>3.317290694012511</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>1.397782859875581</v>
+        <v>1.342802499436939</v>
       </c>
       <c r="E1885" t="n">
-        <v>3.720510895087632</v>
+        <v>3.698518750912176</v>
       </c>
       <c r="F1885" t="n">
-        <v>2.450951804238153</v>
+        <v>2.484030478568096</v>
       </c>
       <c r="G1885" t="n">
-        <v>4.632325257994039</v>
+        <v>4.652172462592005</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240226.xlsx
+++ b/tame_output/ON/bt/strategyON_20240226.xlsx
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153005</v>
+        <v>3.258791981153006</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537424</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074619</v>
+        <v>3.25147557607462</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911637</v>
+        <v>3.233800325911638</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213493</v>
+        <v>3.223539378213494</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416042</v>
+        <v>3.231167537416043</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382326</v>
+        <v>3.235981977382327</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495498</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178245</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207814</v>
+        <v>3.305316798207815</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310983</v>
+        <v>3.284619513310984</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006534</v>
+        <v>3.305849539006535</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309426</v>
+        <v>3.311086391309427</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970907</v>
+        <v>3.304715716970908</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330525</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.30261819419174</v>
+        <v>3.302618194191741</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108642</v>
+        <v>3.305023265108643</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.37443904309412</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.40596051119929</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969598</v>
+        <v>3.424633354969599</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923091</v>
+        <v>3.419979433923092</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297754</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234393</v>
+        <v>3.480688917234394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860582</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.317290694012511</v>
+        <v>3.317290694012512</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
